--- a/data/Plantilla_Calculadora_ESVD_ES.xlsx
+++ b/data/Plantilla_Calculadora_ESVD_ES.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="R9e9c29c118674133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIGURACION" sheetId="2" r:id="R9817050413e8468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_ESVD" sheetId="3" r:id="R80367e73ae3e407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUENTAS_COSTO" sheetId="4" r:id="Rafd081c672fa49d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATALOGOS" sheetId="5" r:id="Raf0541131f374176"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO" sheetId="6" r:id="R25581877cb4e4cb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIES_REFERENCIA" sheetId="7" r:id="R496c604013554889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COSTOS_REFERENCIA" sheetId="8" r:id="R5b2763e5cc5c46b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASOS_VDEP" sheetId="9" r:id="Rfaf2ae61ce344eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECEPTORES_VDEP" sheetId="10" r:id="R1a3d072f0937409f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARIABLES_VDEP" sheetId="11" r:id="Rc6622d309bb6425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="R64002e6fd28049ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIGURACION" sheetId="2" r:id="Rd9880f50435040d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_ESVD" sheetId="3" r:id="R786fcbc300354860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUENTAS_COSTO" sheetId="4" r:id="R99ab2712daf04b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATALOGOS" sheetId="5" r:id="Rceae70866a5c4c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO" sheetId="6" r:id="R3e29a4f1855444c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIES_REFERENCIA" sheetId="7" r:id="R1c44d6f9c2734b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COSTOS_REFERENCIA" sheetId="8" r:id="Rd348faa54dd240ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASOS_VDEP" sheetId="9" r:id="Re8b6cf4338504aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECEPTORES_VDEP" sheetId="10" r:id="Rc6c92d08e24b4fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARIABLES_VDEP" sheetId="11" r:id="R1f4b736d7c0d42b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MULTAS_7317" sheetId="12" r:id="R06308b6888d9482d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,13 +86,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="204" formatCode="0%"/>
     <x:numFmt numFmtId="205" formatCode="[$₡-es-CR]#,##0"/>
+    <x:numFmt numFmtId="206" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="50">
     <x:font>
@@ -376,7 +378,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="63">
+  <x:fills count="67">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -688,6 +690,26 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173A4F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEFEF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF147D80"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="18">
     <x:border/>
@@ -852,7 +874,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="506">
+  <x:cellXfs count="524">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2207,6 +2229,46 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="0" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="47" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="46" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="46" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="44" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="44" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="42" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="42" fillId="66" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="42" fillId="66" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="66" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="66" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="45" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="45" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="45" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3155,6 +3217,18 @@
         <x:v>No usar como tarifa, promedio real ni parámetro oficial. Sustituir por evidencia específica del expediente cuando esté disponible.</x:v>
       </x:c>
     </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="514" t="str">
+        <x:v>Las multas de la Ley 7317 se seleccionan en una pestaña propia de la aplicación. Se muestran separadas del daño y solo se suman en el total final.</x:v>
+      </x:c>
+      <x:c r="B33" s="514"/>
+      <x:c r="C33" s="514"/>
+      <x:c r="D33" s="514"/>
+      <x:c r="E33" s="514"/>
+      <x:c r="F33" s="514"/>
+      <x:c r="G33" s="514"/>
+      <x:c r="H33" s="514"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -3171,6 +3245,7 @@
     <x:mergeCell ref="A30:H30"/>
     <x:mergeCell ref="A31:H31"/>
     <x:mergeCell ref="A32:H32"/>
+    <x:mergeCell ref="A33:H33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5241,6 +5316,1211 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="68" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="46" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="510" t="str">
+        <x:v>Catálogo de multas · Ley N.° 7317</x:v>
+      </x:c>
+      <x:c r="B1" s="510"/>
+      <x:c r="C1" s="510"/>
+      <x:c r="D1" s="510"/>
+      <x:c r="E1" s="510"/>
+      <x:c r="F1" s="510"/>
+      <x:c r="G1" s="510"/>
+      <x:c r="H1" s="510"/>
+      <x:c r="I1" s="510"/>
+      <x:c r="J1" s="510"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="514" t="str">
+        <x:v>La aplicación usa este catálogo para ofrecer casillas de selección. La multa no es un multiplicador del daño ambiental: se calcula y presenta por separado antes de incorporarla al total final.</x:v>
+      </x:c>
+      <x:c r="B2" s="514"/>
+      <x:c r="C2" s="514"/>
+      <x:c r="D2" s="514"/>
+      <x:c r="E2" s="514"/>
+      <x:c r="F2" s="514"/>
+      <x:c r="G2" s="514"/>
+      <x:c r="H2" s="514"/>
+      <x:c r="I2" s="514"/>
+      <x:c r="J2" s="514"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="520" t="str">
+        <x:v>ID_MULTA</x:v>
+      </x:c>
+      <x:c r="B5" s="520" t="str">
+        <x:v>ARTÍCULO</x:v>
+      </x:c>
+      <x:c r="C5" s="520" t="str">
+        <x:v>TIPO</x:v>
+      </x:c>
+      <x:c r="D5" s="520" t="str">
+        <x:v>CONDUCTA</x:v>
+      </x:c>
+      <x:c r="E5" s="520" t="str">
+        <x:v>MÍN_SB</x:v>
+      </x:c>
+      <x:c r="F5" s="520" t="str">
+        <x:v>CENTRAL_SB_SUGERIDO</x:v>
+      </x:c>
+      <x:c r="G5" s="520" t="str">
+        <x:v>MÁX_SB</x:v>
+      </x:c>
+      <x:c r="H5" s="520" t="str">
+        <x:v>OTRAS_CONSECUENCIAS</x:v>
+      </x:c>
+      <x:c r="I5" s="520" t="str">
+        <x:v>FUENTE_OFICIAL</x:v>
+      </x:c>
+      <x:c r="J5" s="520" t="str">
+        <x:v>NOTA_VIGENCIA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="522" t="str">
+        <x:v>L7317-090</x:v>
+      </x:c>
+      <x:c r="B6" s="522" t="str">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C6" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D6" s="522" t="str">
+        <x:v>Extraer o destruir, sin autorización, plantas o sus productos en áreas oficiales de protección o áreas privadas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E6" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="522" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="I6" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J6" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="522" t="str">
+        <x:v>L7317-091A</x:v>
+      </x:c>
+      <x:c r="B7" s="522" t="str">
+        <x:v>91(a)</x:v>
+      </x:c>
+      <x:c r="C7" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D7" s="522" t="str">
+        <x:v>Importar o exportar flora silvestre en peligro, con poblaciones reducidas o incluida en CITES, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E7" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="523" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="G7" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="522" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="I7" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J7" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="522" t="str">
+        <x:v>L7317-091B</x:v>
+      </x:c>
+      <x:c r="B8" s="522" t="str">
+        <x:v>91(b)</x:v>
+      </x:c>
+      <x:c r="C8" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D8" s="522" t="str">
+        <x:v>Importar o exportar productos o subproductos de árboles maderables en peligro, con poblaciones reducidas e incluidos en CITES, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E8" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="523" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H8" s="522" t="str">
+        <x:v>Multa o prisión de 3 a 6 meses.</x:v>
+      </x:c>
+      <x:c r="I8" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J8" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="522" t="str">
+        <x:v>L7317-091C</x:v>
+      </x:c>
+      <x:c r="B9" s="522" t="str">
+        <x:v>91(c)</x:v>
+      </x:c>
+      <x:c r="C9" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D9" s="522" t="str">
+        <x:v>Importar o exportar plantas que no están en peligro de extinción, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E9" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F9" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="523" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H9" s="522" t="str">
+        <x:v>Multa equivalente al 50 % del rango de 1 a 3 salarios base, o prisión de 1 a 3 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="I9" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J9" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="522" t="str">
+        <x:v>L7317-092</x:v>
+      </x:c>
+      <x:c r="B10" s="522" t="str">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C10" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D10" s="522" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar flora protegida, sus productos o subproductos, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E10" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="523" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="G10" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H10" s="522" t="str">
+        <x:v>Multa o prisión de 3 a 6 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="I10" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J10" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="522" t="str">
+        <x:v>L7317-093B</x:v>
+      </x:c>
+      <x:c r="B11" s="522" t="str">
+        <x:v>93(b)</x:v>
+      </x:c>
+      <x:c r="C11" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D11" s="522" t="str">
+        <x:v>Cazar o capturar fauna no amenazada en áreas oficiales o privadas autorizadas, o individuos incluidos en investigación autorizada.</x:v>
+      </x:c>
+      <x:c r="E11" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="523" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G11" s="523" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H11" s="522" t="str">
+        <x:v>Multa o prisión de 6 meses a 1 año; comiso de equipo y piezas.</x:v>
+      </x:c>
+      <x:c r="I11" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J11" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="522" t="str">
+        <x:v>L7317-093C</x:v>
+      </x:c>
+      <x:c r="B12" s="522" t="str">
+        <x:v>93(c)</x:v>
+      </x:c>
+      <x:c r="C12" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D12" s="522" t="str">
+        <x:v>Cazar fauna sujeta a veda que no esté comprendida en los incisos anteriores.</x:v>
+      </x:c>
+      <x:c r="E12" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" s="522" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de armas y piezas.</x:v>
+      </x:c>
+      <x:c r="I12" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J12" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="522" t="str">
+        <x:v>L7317-094</x:v>
+      </x:c>
+      <x:c r="B13" s="522" t="str">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C13" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D13" s="522" t="str">
+        <x:v>Usar sin autorización venenos, materiales peligrosos, explosivos, plaguicidas u otro método capaz de eliminar fauna y poner en peligro su subsistencia regional.</x:v>
+      </x:c>
+      <x:c r="E13" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F13" s="523" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G13" s="523" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H13" s="522" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; pérdida del equipo o material; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="I13" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J13" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="522" t="str">
+        <x:v>L7317-095A</x:v>
+      </x:c>
+      <x:c r="B14" s="522" t="str">
+        <x:v>95(a)</x:v>
+      </x:c>
+      <x:c r="C14" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D14" s="522" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar fauna en peligro o con poblaciones reducidas, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E14" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="523" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G14" s="523" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H14" s="522" t="str">
+        <x:v>Multa o prisión de 1 a 3 años; comiso.</x:v>
+      </x:c>
+      <x:c r="I14" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J14" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="522" t="str">
+        <x:v>L7317-095B</x:v>
+      </x:c>
+      <x:c r="B15" s="522" t="str">
+        <x:v>95(b)</x:v>
+      </x:c>
+      <x:c r="C15" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D15" s="522" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar fauna no amenazada, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E15" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G15" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H15" s="522" t="str">
+        <x:v>Multa o prisión de 4 a 6 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="I15" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J15" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="54" customHeight="1">
+      <x:c r="A16" s="522" t="str">
+        <x:v>L7317-096A</x:v>
+      </x:c>
+      <x:c r="B16" s="522" t="str">
+        <x:v>96(a)</x:v>
+      </x:c>
+      <x:c r="C16" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D16" s="522" t="str">
+        <x:v>Importar o exportar fauna en peligro, con poblaciones reducidas o incluida en CITES, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E16" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F16" s="523" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G16" s="523" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H16" s="522" t="str">
+        <x:v>Multa o prisión de 1 a 3 años; comiso.</x:v>
+      </x:c>
+      <x:c r="I16" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J16" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="54" customHeight="1">
+      <x:c r="A17" s="522" t="str">
+        <x:v>L7317-096B</x:v>
+      </x:c>
+      <x:c r="B17" s="522" t="str">
+        <x:v>96(b)</x:v>
+      </x:c>
+      <x:c r="C17" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D17" s="522" t="str">
+        <x:v>Importar o exportar fauna no amenazada, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E17" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G17" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H17" s="522" t="str">
+        <x:v>Multa o prisión de 4 a 8 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="I17" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J17" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="54" customHeight="1">
+      <x:c r="A18" s="522" t="str">
+        <x:v>L7317-097A</x:v>
+      </x:c>
+      <x:c r="B18" s="522" t="str">
+        <x:v>97, párr. 1</x:v>
+      </x:c>
+      <x:c r="C18" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D18" s="522" t="str">
+        <x:v>Pescar en aguas continentales con explosivos, arbaletas, atarrayas, chinchorros, líneas múltiples, trasmallo u otro método que ponga en peligro la continuidad de las especies.</x:v>
+      </x:c>
+      <x:c r="E18" s="523" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F18" s="523" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="G18" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H18" s="522" t="str">
+        <x:v>Multa o prisión de 2 a 8 meses; comiso del equipo o material.</x:v>
+      </x:c>
+      <x:c r="I18" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J18" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="54" customHeight="1">
+      <x:c r="A19" s="522" t="str">
+        <x:v>L7317-097B</x:v>
+      </x:c>
+      <x:c r="B19" s="522" t="str">
+        <x:v>97, párr. 2</x:v>
+      </x:c>
+      <x:c r="C19" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D19" s="522" t="str">
+        <x:v>Pescar en aguas continentales con venenos, cal o plaguicidas.</x:v>
+      </x:c>
+      <x:c r="E19" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F19" s="523" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G19" s="523" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H19" s="522" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; comiso; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="I19" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J19" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="54" customHeight="1">
+      <x:c r="A20" s="522" t="str">
+        <x:v>L7317-097C</x:v>
+      </x:c>
+      <x:c r="B20" s="522" t="str">
+        <x:v>97, párr. final</x:v>
+      </x:c>
+      <x:c r="C20" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D20" s="522" t="str">
+        <x:v>Dañar poblaciones objetivo de pesca, especies capturadas incidentalmente o ecosistemas de los que dependen.</x:v>
+      </x:c>
+      <x:c r="E20" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F20" s="523" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G20" s="523" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H20" s="522" t="str">
+        <x:v>La norma remite a igual pena del párrafo anterior; confirmar la calificación jurídica del caso.</x:v>
+      </x:c>
+      <x:c r="I20" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J20" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="54" customHeight="1">
+      <x:c r="A21" s="522" t="str">
+        <x:v>L7317-099</x:v>
+      </x:c>
+      <x:c r="B21" s="522" t="str">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C21" s="522" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D21" s="522" t="str">
+        <x:v>Introducir o liberar sin autorización especies exóticas o materiales de control biológico que pongan en peligro la conservación de flora o fauna.</x:v>
+      </x:c>
+      <x:c r="E21" s="523" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F21" s="523" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G21" s="523" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H21" s="522" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; pérdida del equipo o material; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="I21" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J21" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="522" t="str">
+        <x:v>L7317-102</x:v>
+      </x:c>
+      <x:c r="B22" s="522" t="str">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C22" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D22" s="522" t="str">
+        <x:v>Extraer sin autorización plantas o productos, sin fin comercial, en áreas oficiales de protección o áreas privadas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E22" s="523" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F22" s="523" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G22" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H22" s="522" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="I22" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J22" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="522" t="str">
+        <x:v>L7317-103</x:v>
+      </x:c>
+      <x:c r="B23" s="522" t="str">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C23" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D23" s="522" t="str">
+        <x:v>Extraer o comerciar sin autorización raíces o tallos de helechos arborescentes.</x:v>
+      </x:c>
+      <x:c r="E23" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F23" s="523" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G23" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I23" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J23" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="522" t="str">
+        <x:v>L7317-104</x:v>
+      </x:c>
+      <x:c r="B24" s="522" t="str">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C24" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D24" s="522" t="str">
+        <x:v>Extraer o comerciar flora silvestre sin autorización, cuando no exista infracción de mayor gravedad.</x:v>
+      </x:c>
+      <x:c r="E24" s="523" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F24" s="523" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G24" s="523" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H24" s="522" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="I24" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J24" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="522" t="str">
+        <x:v>L7317-105</x:v>
+      </x:c>
+      <x:c r="B25" s="522" t="str">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C25" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D25" s="522" t="str">
+        <x:v>Importar flora silvestre exótica sin autorización.</x:v>
+      </x:c>
+      <x:c r="E25" s="523" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F25" s="523" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G25" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H25" s="522" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="I25" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J25" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="54" customHeight="1">
+      <x:c r="A26" s="522" t="str">
+        <x:v>L7317-106</x:v>
+      </x:c>
+      <x:c r="B26" s="522" t="str">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C26" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D26" s="522" t="str">
+        <x:v>Ingresar sin autorización a áreas de conservación portando armas, herramientas o utensilios útiles para caza, pesca, tala, extracción, captura o trasiego, cuando no haya infracción más grave.</x:v>
+      </x:c>
+      <x:c r="E26" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G26" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I26" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J26" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="54" customHeight="1">
+      <x:c r="A27" s="522" t="str">
+        <x:v>L7317-107</x:v>
+      </x:c>
+      <x:c r="B27" s="522" t="str">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C27" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D27" s="522" t="str">
+        <x:v>Cazar fauna silvestre sin la licencia correspondiente.</x:v>
+      </x:c>
+      <x:c r="E27" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F27" s="523" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G27" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H27" s="522" t="str">
+        <x:v>Multa; pérdida de armas y comiso de piezas.</x:v>
+      </x:c>
+      <x:c r="I27" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J27" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="54" customHeight="1">
+      <x:c r="A28" s="522" t="str">
+        <x:v>L7317-108A</x:v>
+      </x:c>
+      <x:c r="B28" s="522" t="str">
+        <x:v>108, párr. 1</x:v>
+      </x:c>
+      <x:c r="C28" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D28" s="522" t="str">
+        <x:v>Cazar especies permitidas con armas o proyectiles inadecuados.</x:v>
+      </x:c>
+      <x:c r="E28" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F28" s="523" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G28" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="522" t="str">
+        <x:v>Multa; comiso de armas y piezas.</x:v>
+      </x:c>
+      <x:c r="I28" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J28" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="54" customHeight="1">
+      <x:c r="A29" s="522" t="str">
+        <x:v>L7317-108B</x:v>
+      </x:c>
+      <x:c r="B29" s="522" t="str">
+        <x:v>108, párr. 2</x:v>
+      </x:c>
+      <x:c r="C29" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D29" s="522" t="str">
+        <x:v>No reportar ante SINAC las piezas cazadas, pese a contar con autorización para cazar.</x:v>
+      </x:c>
+      <x:c r="E29" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F29" s="523" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G29" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="522" t="str">
+        <x:v>Igual pena del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="I29" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J29" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="54" customHeight="1">
+      <x:c r="A30" s="522" t="str">
+        <x:v>L7317-109A</x:v>
+      </x:c>
+      <x:c r="B30" s="522" t="str">
+        <x:v>109, párr. 1</x:v>
+      </x:c>
+      <x:c r="C30" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D30" s="522" t="str">
+        <x:v>Exceder los límites reglamentarios de un permiso de caza de control o pesca respecto de piezas, tamaños, especies o zonas.</x:v>
+      </x:c>
+      <x:c r="E30" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F30" s="523" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="G30" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H30" s="522" t="str">
+        <x:v>Multa; comiso de piezas o derivados y pérdida del equipo o material.</x:v>
+      </x:c>
+      <x:c r="I30" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J30" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="54" customHeight="1">
+      <x:c r="A31" s="522" t="str">
+        <x:v>L7317-109B</x:v>
+      </x:c>
+      <x:c r="B31" s="522" t="str">
+        <x:v>109, párr. 2</x:v>
+      </x:c>
+      <x:c r="C31" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D31" s="522" t="str">
+        <x:v>Usar para fines distintos las piezas obtenidas con permisos de caza de subsistencia o control, o de colecta científica.</x:v>
+      </x:c>
+      <x:c r="E31" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F31" s="523" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="G31" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H31" s="522" t="str">
+        <x:v>Igual pena del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="I31" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J31" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="54" customHeight="1">
+      <x:c r="A32" s="522" t="str">
+        <x:v>L7317-110A</x:v>
+      </x:c>
+      <x:c r="B32" s="522" t="str">
+        <x:v>110, supuesto 1</x:v>
+      </x:c>
+      <x:c r="C32" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D32" s="522" t="str">
+        <x:v>Mantener en cautiverio o como mascota, sin autorización, fauna en peligro de extinción o con poblaciones reducidas.</x:v>
+      </x:c>
+      <x:c r="E32" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F32" s="523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G32" s="523" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H32" s="522" t="str">
+        <x:v>Multa y comiso de los animales.</x:v>
+      </x:c>
+      <x:c r="I32" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J32" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="522" t="str">
+        <x:v>L7317-110B</x:v>
+      </x:c>
+      <x:c r="B33" s="522" t="str">
+        <x:v>110, supuesto 2</x:v>
+      </x:c>
+      <x:c r="C33" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D33" s="522" t="str">
+        <x:v>Mantener en cautiverio o como mascota, sin autorización, fauna no amenazada ni con poblaciones reducidas.</x:v>
+      </x:c>
+      <x:c r="E33" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F33" s="523" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G33" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H33" s="522" t="str">
+        <x:v>Multa y comiso de los animales.</x:v>
+      </x:c>
+      <x:c r="I33" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J33" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="522" t="str">
+        <x:v>L7317-111A</x:v>
+      </x:c>
+      <x:c r="B34" s="522" t="str">
+        <x:v>111, párr. 1</x:v>
+      </x:c>
+      <x:c r="C34" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D34" s="522" t="str">
+        <x:v>Dedicarse comercialmente a la taxidermia o al procesamiento de pieles de fauna silvestre sin autorización.</x:v>
+      </x:c>
+      <x:c r="E34" s="523" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F34" s="523" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G34" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H34" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I34" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J34" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="54" customHeight="1">
+      <x:c r="A35" s="522" t="str">
+        <x:v>L7317-111B</x:v>
+      </x:c>
+      <x:c r="B35" s="522" t="str">
+        <x:v>111, párr. 2</x:v>
+      </x:c>
+      <x:c r="C35" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D35" s="522" t="str">
+        <x:v>No llevar el libro de control exigido para taxidermia o procesamiento comercial autorizado.</x:v>
+      </x:c>
+      <x:c r="E35" s="523" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F35" s="523" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G35" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H35" s="522" t="str">
+        <x:v>Igual sanción del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="I35" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J35" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="54" customHeight="1">
+      <x:c r="A36" s="522" t="str">
+        <x:v>L7317-112</x:v>
+      </x:c>
+      <x:c r="B36" s="522" t="str">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C36" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D36" s="522" t="str">
+        <x:v>Dejar voluntariamente de buscar las piezas cazadas o pescadas y provocar desperdicio del recurso.</x:v>
+      </x:c>
+      <x:c r="E36" s="523" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F36" s="523" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G36" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H36" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I36" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J36" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="54" customHeight="1">
+      <x:c r="A37" s="522" t="str">
+        <x:v>L7317-113</x:v>
+      </x:c>
+      <x:c r="B37" s="522" t="str">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C37" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D37" s="522" t="str">
+        <x:v>Pescar sin la licencia correspondiente.</x:v>
+      </x:c>
+      <x:c r="E37" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F37" s="523" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G37" s="523" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H37" s="522" t="str">
+        <x:v>Multa; pérdida del equipo señalado y comiso de piezas.</x:v>
+      </x:c>
+      <x:c r="I37" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J37" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="54" customHeight="1">
+      <x:c r="A38" s="522" t="str">
+        <x:v>L7317-114</x:v>
+      </x:c>
+      <x:c r="B38" s="522" t="str">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C38" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D38" s="522" t="str">
+        <x:v>Exceder límites de pesca respecto de tamaños, cantidades, especies o zonas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E38" s="523" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F38" s="523" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G38" s="523" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H38" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I38" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J38" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="54" customHeight="1">
+      <x:c r="A39" s="522" t="str">
+        <x:v>L7317-115</x:v>
+      </x:c>
+      <x:c r="B39" s="522" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C39" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D39" s="522" t="str">
+        <x:v>Pescar en tiempo de veda.</x:v>
+      </x:c>
+      <x:c r="E39" s="523" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F39" s="523" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G39" s="523" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" s="522" t="str">
+        <x:v>Multa y comiso del equipo y las piezas.</x:v>
+      </x:c>
+      <x:c r="I39" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J39" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="54" customHeight="1">
+      <x:c r="A40" s="522" t="str">
+        <x:v>L7317-116</x:v>
+      </x:c>
+      <x:c r="B40" s="522" t="str">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C40" s="522" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D40" s="522" t="str">
+        <x:v>Suministrar sin autorización alimentos o sustancias no autorizadas a la fauna silvestre.</x:v>
+      </x:c>
+      <x:c r="E40" s="523" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F40" s="523" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G40" s="523" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H40" s="522" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="I40" s="522" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="J40" s="522" t="str">
+        <x:v>Verificar texto vigente y calificación jurídica antes de seleccionar.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -5522,28 +6802,64 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="408"/>
-      <x:c r="B15" s="408"/>
-      <x:c r="C15" s="409"/>
-      <x:c r="D15" s="409"/>
-      <x:c r="E15" s="409"/>
-      <x:c r="F15"/>
+      <x:c r="A15" s="507" t="str">
+        <x:v>salario_base_ley_7337</x:v>
+      </x:c>
+      <x:c r="B15" s="507" t="n">
+        <x:v>462200</x:v>
+      </x:c>
+      <x:c r="C15" s="409" t="str">
+        <x:v>CRC</x:v>
+      </x:c>
+      <x:c r="D15" s="409" t="str">
+        <x:v>Salario base 2026 usado para convertir los rangos de multas de la Ley 7317.</x:v>
+      </x:c>
+      <x:c r="E15" s="409" t="str">
+        <x:v>Equipo jurídico</x:v>
+      </x:c>
+      <x:c r="F15" s="409" t="str">
+        <x:v>https://pj.poder-judicial.go.cr/index.php/component/content/article/2333-poder-judicial-fija-en-462-200-00-el-salario-base-para-multas-y-penas-por-la-comision-de-figuras-delictivas-en-el-2026?Itemid=409&amp;catid=8</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="408"/>
-      <x:c r="B16" s="408"/>
-      <x:c r="C16" s="409"/>
-      <x:c r="D16" s="409"/>
-      <x:c r="E16" s="409"/>
-      <x:c r="F16"/>
+      <x:c r="A16" s="507" t="str">
+        <x:v>anio_salario_base</x:v>
+      </x:c>
+      <x:c r="B16" s="507" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C16" s="409" t="str">
+        <x:v>Año</x:v>
+      </x:c>
+      <x:c r="D16" s="409" t="str">
+        <x:v>Año del salario base usado en la pestaña de multas.</x:v>
+      </x:c>
+      <x:c r="E16" s="409" t="str">
+        <x:v>Equipo jurídico</x:v>
+      </x:c>
+      <x:c r="F16" s="409" t="str">
+        <x:v>Actualizar cuando el Poder Judicial publique un nuevo salario base.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="408"/>
-      <x:c r="B17" s="408"/>
-      <x:c r="C17" s="409"/>
-      <x:c r="D17" s="409"/>
-      <x:c r="E17" s="409"/>
-      <x:c r="F17"/>
+      <x:c r="A17" s="507" t="str">
+        <x:v>fuente_ley_7317</x:v>
+      </x:c>
+      <x:c r="B17" s="507" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="C17" s="409" t="str">
+        <x:v>URL</x:v>
+      </x:c>
+      <x:c r="D17" s="409" t="str">
+        <x:v>Texto consolidado de la Ley 7317 consultado para el catálogo de multas.</x:v>
+      </x:c>
+      <x:c r="E17" s="409" t="str">
+        <x:v>Equipo jurídico</x:v>
+      </x:c>
+      <x:c r="F17" s="409" t="str">
+        <x:v>Verificar vigencia antes de emitir una valoración definitiva.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="408"/>
@@ -5740,9 +7056,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc4e958d18f74455"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65c279c273948f5"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23ce389371584738"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc99108a5fd9345e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15022,9 +16338,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb64ec1f2f984601"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R322798fb54654370"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b06470acdc34673"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7c9924f9a74c60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15311,7 +16627,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af777c2d5454d16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4302569818e44624"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17251,7 +18567,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra35889444ce34d60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fbc9cf698204619"/>
   </x:tableParts>
 </x:worksheet>
 </file>
